--- a/SGC-CKN/Excel/9851cf38-4562-43cb-ad0f-bed779642f13_Đại_trà_C2-431_D1200_08-09-2026.xlsx
+++ b/SGC-CKN/Excel/9851cf38-4562-43cb-ad0f-bed779642f13_Đại_trà_C2-431_D1200_08-09-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:00 08/09/2026</t>
+    <t>14:00 08/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -189,12 +189,8 @@
     <t>Cuội sỏi lẫn cát sạn, dăm sạn, đa màu sắc, trạng thái rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">10:03
-08/09/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:00
-08/09/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>Kết thúc khoan</t>
@@ -1473,10 +1469,10 @@
         <v>54</v>
       </c>
       <c r="D19" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>55</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>56</v>
       </c>
       <c r="F19" s="31">
         <v>-75.1</v>
@@ -1494,12 +1490,12 @@
         <v>0.63</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
@@ -1605,31 +1601,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,7 +1891,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="37" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/9851cf38-4562-43cb-ad0f-bed779642f13_Đại_trà_C2-431_D1200_08-09-2026.xlsx
+++ b/SGC-CKN/Excel/9851cf38-4562-43cb-ad0f-bed779642f13_Đại_trà_C2-431_D1200_08-09-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:00 08/04/2026</t>
+    <t>14:09 08/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -189,7 +189,7 @@
     <t>Cuội sỏi lẫn cát sạn, dăm sạn, đa màu sắc, trạng thái rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">14:00
+    <t xml:space="preserve">14:09
 08/04/2026</t>
   </si>
   <si>
@@ -1481,13 +1481,13 @@
         <v>-77.6</v>
       </c>
       <c r="H19" s="31">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I19" s="31">
         <v>2.5</v>
       </c>
       <c r="J19" s="34">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>56</v>
@@ -1880,13 +1880,13 @@
         <v>-77.6</v>
       </c>
       <c r="G10" s="31">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H10" s="31">
         <v>2.5</v>
       </c>
       <c r="I10" s="34">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1909,13 +1909,13 @@
         <v>-77.6</v>
       </c>
       <c r="G11" s="37">
-        <v>15.75</v>
+        <v>15.9</v>
       </c>
       <c r="H11" s="37">
         <v>76</v>
       </c>
       <c r="I11" s="37">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>
